--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487899_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487899_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1312</v>
+        <v>2.1906</v>
       </c>
       <c r="E2" t="n">
-        <v>1.194</v>
+        <v>-0.3062</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9372</v>
+        <v>2.4968</v>
       </c>
       <c r="G2" t="n">
         <v>-1.4917</v>
@@ -610,13 +610,13 @@
         <v>1.6649</v>
       </c>
       <c r="S2" t="n">
-        <v>3.934</v>
+        <v>1.9934</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6832</v>
+        <v>1.1831</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2508</v>
+        <v>0.8104</v>
       </c>
       <c r="V2" t="n">
         <v>2.1051</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. ORDOÑEZ OCHOA</t>
+          <t>P. MARIN FONTAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1706</v>
+        <v>1.8581</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2456</v>
+        <v>4.2113</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4162</v>
+        <v>-2.3531</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5622</v>
+        <v>1.949</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.4455</v>
+        <v>-0.6627999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0077</v>
+        <v>2.6117</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4195</v>
+        <v>3.0025</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.335</v>
+        <v>0.7867</v>
       </c>
       <c r="L3" t="n">
-        <v>1.7545</v>
+        <v>2.2158</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1428</v>
+        <v>-1.0535</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1105</v>
+        <v>-1.4495</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2532</v>
+        <v>0.396</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6649</v>
+        <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0378</v>
+        <v>0.1173</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0438</v>
+        <v>-0.0857</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0059</v>
+        <v>0.203</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9376</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.4599</v>
+        <v>2.3351</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3975</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. MARIN FONTAN</t>
+          <t>I. ORDOÑEZ OCHOA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1374</v>
+        <v>1.5611</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4612</v>
+        <v>-0.0312</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3238</v>
+        <v>1.5923</v>
       </c>
       <c r="G4" t="n">
-        <v>1.949</v>
+        <v>2.5622</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6627999999999999</v>
+        <v>-0.4455</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6117</v>
+        <v>3.0077</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0025</v>
+        <v>1.4195</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7867</v>
+        <v>-0.335</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2158</v>
+        <v>1.7545</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0535</v>
+        <v>1.1428</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4495</v>
+        <v>-0.1105</v>
       </c>
       <c r="O4" t="n">
-        <v>0.396</v>
+        <v>1.2532</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6035</v>
+        <v>0.3526</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8358</v>
+        <v>0.1705</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2323</v>
+        <v>0.1821</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-0.9376</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3351</v>
+        <v>0.4599</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3351</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. GARCIA-ABRIL GUERRERO</t>
+          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8237</v>
+        <v>0.582</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3206</v>
+        <v>0.9067</v>
       </c>
       <c r="F5" t="n">
-        <v>0.503</v>
+        <v>-0.3247</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4226</v>
+        <v>1.4879</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5907</v>
+        <v>0.6952</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8319</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9574</v>
+        <v>1.0186</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5542</v>
+        <v>0.9402</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5968</v>
+        <v>0.0784</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4652</v>
+        <v>0.4693</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.9636</v>
+        <v>-0.245</v>
       </c>
       <c r="O5" t="n">
-        <v>1.4287</v>
+        <v>0.7144</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.4974</v>
+        <v>0.8325</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.1218</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S5" t="n">
-        <v>2.836</v>
+        <v>-0.3409</v>
       </c>
       <c r="T5" t="n">
-        <v>2.025</v>
+        <v>-0.1119</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8110000000000001</v>
+        <v>-0.229</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.9376</v>
+        <v>-1.3975</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4599</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>-1.3975</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. QUEREJETA MARTINEZ DE ARENAZA</t>
+          <t>I. HANEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1622</v>
+        <v>-0.1333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6924</v>
+        <v>-3.3664</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5302</v>
+        <v>3.2331</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4879</v>
+        <v>0.1074</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6952</v>
+        <v>3.7715</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7927999999999999</v>
+        <v>-3.6641</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0186</v>
+        <v>-1.215</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9402</v>
+        <v>3.882</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0784</v>
+        <v>-5.097</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4693</v>
+        <v>1.3224</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.245</v>
+        <v>-0.1105</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7144</v>
+        <v>1.4328</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8325</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7607</v>
+        <v>0.4024</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3262</v>
+        <v>-0.0733</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4345</v>
+        <v>0.4757</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3975</v>
+        <v>0.8137</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0437</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.3975</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1393</v>
+        <v>-0.1496</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0765</v>
+        <v>0.0306</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.1802</v>
       </c>
       <c r="G7" t="n">
         <v>-0.1074</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3888</v>
+        <v>-0.3991</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3915</v>
+        <v>-0.2843</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0026</v>
+        <v>-0.1148</v>
       </c>
       <c r="V7" t="n">
         <v>1.3975</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. HANEY</t>
+          <t>J. GARCIA-ABRIL GUERRERO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0008</v>
+        <v>-0.3272</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.1165</v>
+        <v>-0.5366</v>
       </c>
       <c r="F8" t="n">
-        <v>3.1156</v>
+        <v>0.2095</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1074</v>
+        <v>1.4226</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7715</v>
+        <v>0.5907</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.6641</v>
+        <v>0.8319</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.215</v>
+        <v>0.9574</v>
       </c>
       <c r="K8" t="n">
-        <v>3.882</v>
+        <v>1.5542</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.097</v>
+        <v>-0.5968</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3224</v>
+        <v>0.4652</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1105</v>
+        <v>-0.9636</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4328</v>
+        <v>1.4287</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.4568</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q8" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4651</v>
+        <v>1.6852</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8234</v>
+        <v>1.1678</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3583</v>
+        <v>0.5174</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8137</v>
+        <v>-0.9376</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0437</v>
+        <v>0.4599</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.23</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.094</v>
+        <v>-3.567</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5188</v>
+        <v>-1.1973</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.5752</v>
+        <v>-2.3697</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2152</v>
@@ -1234,13 +1234,13 @@
         <v>1.0406</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6707</v>
+        <v>-0.1437</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5129</v>
+        <v>-0.1914</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1578</v>
+        <v>0.0477</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1675</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4339</v>
+        <v>-5.2577</v>
       </c>
       <c r="E11" t="n">
         <v>-2.2689</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1649</v>
+        <v>-2.9888</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7684</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0411</v>
+        <v>0.135</v>
       </c>
       <c r="T11" t="n">
         <v>0.2048</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2459</v>
+        <v>-0.0698</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5838</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.825200000000001</v>
+        <v>-5.825299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.351800000000001</v>
+        <v>-3.3517</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4735</v>
+        <v>-2.4734</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.164</v>
+        <v>-2.164000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.592599999999999</v>
+        <v>-3.5926</v>
       </c>
       <c r="I12" t="n">
         <v>1.4288</v>
@@ -1366,7 +1366,7 @@
         <v>1.5939</v>
       </c>
       <c r="K12" t="n">
-        <v>6.0843</v>
+        <v>6.084300000000001</v>
       </c>
       <c r="L12" t="n">
         <v>-4.4904</v>
@@ -1378,7 +1378,7 @@
         <v>-9.677200000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>5.919000000000001</v>
+        <v>5.919</v>
       </c>
       <c r="P12" t="n">
         <v>-7.283999999999999</v>
@@ -1390,10 +1390,10 @@
         <v>8.3247</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1004</v>
+        <v>4.1003</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1718</v>
+        <v>2.172</v>
       </c>
       <c r="U12" t="n">
         <v>1.9284</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.7131</v>
+        <v>8.325799999999999</v>
       </c>
       <c r="E13" t="n">
         <v>7.8828</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1697</v>
+        <v>0.4429</v>
       </c>
       <c r="G13" t="n">
         <v>4.2234</v>
@@ -1468,13 +1468,13 @@
         <v>2.4974</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3427</v>
+        <v>-0.7301</v>
       </c>
       <c r="T13" t="n">
         <v>-0.5129</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8298</v>
+        <v>-0.2172</v>
       </c>
       <c r="V13" t="n">
         <v>2.3351</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3422</v>
+        <v>3.1471</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5023</v>
+        <v>1.2524</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8399</v>
+        <v>1.8947</v>
       </c>
       <c r="G14" t="n">
         <v>2.3481</v>
@@ -1546,13 +1546,13 @@
         <v>1.8731</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8383</v>
+        <v>-0.0334</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0844</v>
+        <v>-0.3343</v>
       </c>
       <c r="U14" t="n">
-        <v>0.246</v>
+        <v>0.3008</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9123</v>
+        <v>2.4354</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2198</v>
+        <v>1.5412</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6926</v>
+        <v>0.8942</v>
       </c>
       <c r="G15" t="n">
         <v>0.0104</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6382</v>
+        <v>-1.1151</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7177</v>
+        <v>-0.3962</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9205</v>
+        <v>-0.7189</v>
       </c>
       <c r="V15" t="n">
         <v>1.8751</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.6992</v>
+        <v>0.9618</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3948</v>
+        <v>-1.3592</v>
       </c>
       <c r="F16" t="n">
-        <v>2.094</v>
+        <v>2.321</v>
       </c>
       <c r="G16" t="n">
         <v>-1.4882</v>
@@ -1702,13 +1702,13 @@
         <v>1.6649</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0386</v>
+        <v>0.3012</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2421</v>
+        <v>0.2777</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2035</v>
+        <v>0.0235</v>
       </c>
       <c r="V16" t="n">
         <v>2.565</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1525</v>
+        <v>0.6546</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5279</v>
+        <v>2.0165</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6804</v>
+        <v>-1.3619</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9452</v>
+        <v>3.1947</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9339</v>
+        <v>4.5499</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9887</v>
+        <v>-1.3553</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.3042</v>
+        <v>3.0805</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.2561</v>
+        <v>4.5092</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0482</v>
+        <v>-1.4287</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3591</v>
+        <v>0.1142</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6778</v>
+        <v>0.0407</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0369</v>
+        <v>0.0735</v>
       </c>
       <c r="P17" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0406</v>
+        <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7033</v>
+        <v>-0.4131</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7763</v>
+        <v>-0.2533</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.073</v>
+        <v>-0.1598</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3538</v>
+        <v>-2.3351</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3538</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3919</v>
+        <v>0.193</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6951</v>
+        <v>-1.278</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3032</v>
+        <v>1.471</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1947</v>
+        <v>-0.9452</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5499</v>
+        <v>-1.9339</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3553</v>
+        <v>0.9887</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0805</v>
+        <v>-1.3042</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5092</v>
+        <v>-1.2561</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4287</v>
+        <v>-0.0482</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1142</v>
+        <v>0.3591</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0407</v>
+        <v>-0.6778</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0735</v>
+        <v>1.0369</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2487</v>
+        <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.2562</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5748</v>
+        <v>0.0262</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1011</v>
+        <v>-0.2824</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.3351</v>
+        <v>0.3538</v>
       </c>
       <c r="W18" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.565</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2398</v>
+        <v>0.0412</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.571</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.6688</v>
+        <v>-0.0307</v>
       </c>
       <c r="G19" t="n">
         <v>0.7739</v>
@@ -1936,13 +1936,13 @@
         <v>2.2893</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0949</v>
+        <v>-0.8139</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2272</v>
+        <v>-0.5843</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8677</v>
+        <v>-0.2296</v>
       </c>
       <c r="V19" t="n">
         <v>-1.1675</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>V. HRABAR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.553</v>
+        <v>-2.3471</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.2376</v>
+        <v>-2.7526</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6846</v>
+        <v>0.4055</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2593</v>
+        <v>-3.3169</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.531</v>
+        <v>-1.791</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7903</v>
+        <v>-1.5259</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.104</v>
+        <v>-2.6064</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1431</v>
+        <v>-1.2561</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0392</v>
+        <v>-1.3504</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3632</v>
+        <v>-0.7105</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3879</v>
+        <v>-0.5349</v>
       </c>
       <c r="O20" t="n">
-        <v>0.7511</v>
+        <v>-0.1755</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0202</v>
+        <v>-0.2571</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5748</v>
+        <v>-0.1462</v>
       </c>
       <c r="U20" t="n">
-        <v>0.595</v>
+        <v>-0.1109</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6899</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.704</v>
+        <v>-2.4855</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9139</v>
+        <v>-3.0233</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7901</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.8956</v>
+        <v>0.2593</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8741</v>
+        <v>-0.531</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.0215</v>
+        <v>0.7903</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.3606</v>
+        <v>-0.104</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.335</v>
+        <v>-0.1431</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.0256</v>
+        <v>0.0392</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.535</v>
+        <v>0.3632</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5391</v>
+        <v>-0.3879</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0041</v>
+        <v>0.7511</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.6649</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-2.0812</v>
+      </c>
+      <c r="R21" t="n">
         <v>0.4162</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-1.0406</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.4568</v>
-      </c>
       <c r="S21" t="n">
-        <v>1.5266</v>
+        <v>0.0877</v>
       </c>
       <c r="T21" t="n">
-        <v>1.3197</v>
+        <v>-0.3605</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2069</v>
+        <v>0.4482</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.7513</v>
+        <v>-1.1675</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>-0.4776</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.9188</v>
+        <v>-0.6899</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>V. HRABAR</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8892</v>
+        <v>-3.6723</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.1812</v>
+        <v>-1.8783</v>
       </c>
       <c r="F22" t="n">
-        <v>0.292</v>
+        <v>-1.794</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.3169</v>
+        <v>-2.8956</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.791</v>
+        <v>-0.8741</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.5259</v>
+        <v>-2.0215</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.6064</v>
+        <v>-2.3606</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2561</v>
+        <v>-0.335</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3504</v>
+        <v>-2.0256</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7105</v>
+        <v>-0.535</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5349</v>
+        <v>-0.5391</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1755</v>
+        <v>0.0041</v>
       </c>
       <c r="P22" t="n">
-        <v>1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R22" t="n">
         <v>1.4568</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7992</v>
+        <v>0.5583</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5748</v>
+        <v>0.3553</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2244</v>
+        <v>0.203</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.1675</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.23</v>
+        <v>-2.9188</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>5.825199999999997</v>
+        <v>7.254</v>
       </c>
       <c r="E23" t="n">
-        <v>2.473599999999999</v>
+        <v>2.4734</v>
       </c>
       <c r="F23" t="n">
-        <v>3.3517</v>
+        <v>4.7805</v>
       </c>
       <c r="G23" t="n">
         <v>2.1639</v>
@@ -2221,7 +2221,7 @@
         <v>-1.4288</v>
       </c>
       <c r="J23" t="n">
-        <v>3.757799999999999</v>
+        <v>3.7578</v>
       </c>
       <c r="K23" t="n">
         <v>9.677099999999999</v>
@@ -2248,13 +2248,13 @@
         <v>15.6087</v>
       </c>
       <c r="S23" t="n">
-        <v>-4.100499999999999</v>
+        <v>-2.6717</v>
       </c>
       <c r="T23" t="n">
         <v>-1.9285</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.1721</v>
+        <v>-0.7432999999999998</v>
       </c>
       <c r="V23" t="n">
         <v>0.4775999999999998</v>
